--- a/resurse/oferte/cereri/cerere-oferta-pepiniera-selficom.xlsx
+++ b/resurse/oferte/cereri/cerere-oferta-pepiniera-selficom.xlsx
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
